--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486538_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486538_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2416</v>
+        <v>5.8197</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5625</v>
+        <v>4.233</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6791</v>
+        <v>1.5867</v>
       </c>
       <c r="G2" t="n">
         <v>6.4579</v>
@@ -610,13 +610,13 @@
         <v>1.7401</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3463</v>
+        <v>-0.7682</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1524</v>
+        <v>-0.4819</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1939</v>
+        <v>-0.2863</v>
       </c>
       <c r="V2" t="n">
         <v>0.5649999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1245</v>
+        <v>3.4885</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8622</v>
+        <v>2.8564</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2623</v>
+        <v>0.6322</v>
       </c>
       <c r="G3" t="n">
         <v>3.0798</v>
@@ -688,13 +688,13 @@
         <v>0.87</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6972</v>
+        <v>0.0613</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4937</v>
+        <v>0.4879</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7965</v>
+        <v>-0.4266</v>
       </c>
       <c r="V3" t="n">
         <v>0.5649999999999999</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>H. ATENCIA SUAREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9649</v>
+        <v>3.4648</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5861</v>
+        <v>2.6185</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3788</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1583</v>
+        <v>-2.294</v>
       </c>
       <c r="H4" t="n">
-        <v>0.52</v>
+        <v>-2.153</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6383</v>
+        <v>-0.141</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.056</v>
+        <v>-2.2755</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.0521</v>
+        <v>-3.0437</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9961</v>
+        <v>0.7682</v>
       </c>
       <c r="M4" t="n">
-        <v>1.2143</v>
+        <v>-0.0185</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5722</v>
+        <v>0.8907</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3578</v>
+        <v>-0.9093</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.1751</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0875</v>
+        <v>2.1751</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2416</v>
+        <v>-1.3059</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5997</v>
+        <v>-0.7559</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6419</v>
+        <v>-0.5501</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5649999999999999</v>
+        <v>4.8897</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>5.6499</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>H. ATENCIA SUAREZ</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3867</v>
+        <v>2.2713</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8795</v>
+        <v>0.139</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5072</v>
+        <v>2.1322</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.294</v>
+        <v>1.1583</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.153</v>
+        <v>0.52</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.141</v>
+        <v>0.6383</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.2755</v>
+        <v>-0.056</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.0437</v>
+        <v>-1.0521</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7682</v>
+        <v>0.9961</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0185</v>
+        <v>1.2143</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8907</v>
+        <v>1.5722</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9093</v>
+        <v>-0.3578</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1751</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1751</v>
+        <v>1.0875</v>
       </c>
       <c r="S5" t="n">
-        <v>-2.384</v>
+        <v>0.548</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4949</v>
+        <v>0.1526</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8892</v>
+        <v>0.3953</v>
       </c>
       <c r="V5" t="n">
-        <v>4.8897</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>5.6499</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.7602</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. IZAW BOLAVIE</t>
+          <t>J. ROBERTS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8829</v>
+        <v>1.7562</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9718</v>
+        <v>1.4215</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9111</v>
+        <v>0.3347</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1749</v>
+        <v>2.0097</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9033</v>
+        <v>1.2925</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7284</v>
+        <v>0.7171</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1575</v>
+        <v>1.5364</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6840000000000001</v>
+        <v>1.4599</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8415</v>
+        <v>0.0765</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0174</v>
+        <v>0.4732</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5872</v>
+        <v>-0.1674</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.5698</v>
+        <v>0.6407</v>
       </c>
       <c r="P6" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5225</v>
+        <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5982</v>
+        <v>0.1592</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6414</v>
+        <v>-0.1574</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0432</v>
+        <v>0.3166</v>
       </c>
       <c r="V6" t="n">
+        <v>-0.1952</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X6" t="n">
         <v>-1.3252</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.7395</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.5857</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ROBERTS</t>
+          <t>J. FELIU ESPEJO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6722</v>
+        <v>-0.4315</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9059</v>
+        <v>-0.2859</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7662</v>
+        <v>-0.1456</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0097</v>
+        <v>0.2673</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2925</v>
+        <v>-0.3893</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7171</v>
+        <v>0.6566</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5364</v>
+        <v>-0.2394</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4599</v>
+        <v>-0.8514</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0765</v>
+        <v>0.612</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4732</v>
+        <v>0.5067</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1674</v>
+        <v>0.4621</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6407</v>
+        <v>0.0446</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.2175</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0752</v>
+        <v>-0.0463</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7482</v>
+        <v>0.0427</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>1.13</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3252</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. FELIU ESPEJO</t>
+          <t>A. IZAW BOLAVIE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0086</v>
+        <v>-0.5179</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8014</v>
+        <v>-1.1516</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2072</v>
+        <v>0.6337</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2673</v>
+        <v>0.1749</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3893</v>
+        <v>0.9033</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6566</v>
+        <v>-0.7284</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2394</v>
+        <v>0.1575</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8514</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.612</v>
+        <v>0.8415</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5067</v>
+        <v>0.0174</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4621</v>
+        <v>1.5872</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0446</v>
+        <v>-1.5698</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>0.435</v>
+        <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6234</v>
+        <v>0.1974</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6044</v>
+        <v>0.5179</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.019</v>
+        <v>-0.3206</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
       <c r="W8" t="n">
-        <v>1.13</v>
+        <v>-0.7395</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.13</v>
+        <v>-0.5857</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. DIKE EGUN</t>
+          <t>A. URDIAIN LABAYEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.5805</v>
+        <v>-3.919</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5659</v>
+        <v>-6.865</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0147</v>
+        <v>2.946</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.1252</v>
+        <v>-3.2661</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6206</v>
+        <v>0.4712</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.5045</v>
+        <v>-3.7372</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.6995</v>
+        <v>-4.3751</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6173</v>
+        <v>-1.0156</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0822</v>
+        <v>-3.3595</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4257</v>
+        <v>1.109</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0033</v>
+        <v>1.4868</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4224</v>
+        <v>-0.3778</v>
       </c>
       <c r="P9" t="n">
-        <v>1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6305</v>
+        <v>-1.175</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8663999999999999</v>
+        <v>-0.3148</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.764</v>
+        <v>-0.8601</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.13</v>
+        <v>0.7395</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. URDIAIN LABAYEN</t>
+          <t>G. DIKE EGUN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.0973</v>
+        <v>-4.0034</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.8276</v>
+        <v>-3.0504</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7302</v>
+        <v>-0.953</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.2661</v>
+        <v>-3.1252</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4712</v>
+        <v>-0.6206</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.7372</v>
+        <v>-2.5045</v>
       </c>
       <c r="J10" t="n">
-        <v>-4.3751</v>
+        <v>-2.6995</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.0156</v>
+        <v>-0.6173</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.3595</v>
+        <v>-2.0822</v>
       </c>
       <c r="M10" t="n">
-        <v>1.109</v>
+        <v>-0.4257</v>
       </c>
       <c r="N10" t="n">
-        <v>1.4868</v>
+        <v>-0.0033</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3778</v>
+        <v>-0.4224</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.3533</v>
+        <v>-1.0533</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2774</v>
+        <v>-0.3509</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0759</v>
+        <v>-0.7024</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>7.586399999999998</v>
+        <v>7.9287</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4269000000000007</v>
+        <v>-0.08450000000000024</v>
       </c>
       <c r="F11" t="n">
-        <v>8.013</v>
+        <v>8.013200000000001</v>
       </c>
       <c r="G11" t="n">
         <v>4.462600000000002</v>
       </c>
       <c r="H11" t="n">
-        <v>9.032599999999999</v>
+        <v>9.0326</v>
       </c>
       <c r="I11" t="n">
         <v>-4.569900000000001</v>
@@ -1291,7 +1291,7 @@
         <v>1.188499999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0759000000000003</v>
+        <v>0.07589999999999986</v>
       </c>
       <c r="M11" t="n">
         <v>3.1981</v>
@@ -1312,13 +1312,13 @@
         <v>11.9628</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.7253</v>
+        <v>-3.3828</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.3336</v>
+        <v>-0.9913999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.3916</v>
+        <v>-2.3915</v>
       </c>
       <c r="V11" t="n">
         <v>4.673800000000001</v>
@@ -1327,7 +1327,7 @@
         <v>9.430399999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.756599999999999</v>
+        <v>-4.7566</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.3196</v>
+        <v>4.8667</v>
       </c>
       <c r="E12" t="n">
-        <v>4.1259</v>
+        <v>2.673</v>
       </c>
       <c r="F12" t="n">
         <v>2.1937</v>
@@ -1390,10 +1390,10 @@
         <v>1.0875</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2352</v>
+        <v>0.7823</v>
       </c>
       <c r="T12" t="n">
-        <v>2.0333</v>
+        <v>0.5804</v>
       </c>
       <c r="U12" t="n">
         <v>0.2019</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.7391</v>
+        <v>2.6511</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6773</v>
+        <v>-0.0067</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4164</v>
+        <v>2.6579</v>
       </c>
       <c r="G13" t="n">
         <v>1.2665</v>
@@ -1468,13 +1468,13 @@
         <v>1.0875</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6149</v>
+        <v>0.2971</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8099</v>
+        <v>-0.1394</v>
       </c>
       <c r="U13" t="n">
-        <v>0.195</v>
+        <v>0.4365</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B. COULIBALY</t>
+          <t>E. POLANCO TAVAREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7142</v>
+        <v>0.9406</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0377</v>
+        <v>-0.9811</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3235</v>
+        <v>1.9217</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9224</v>
+        <v>-0.2566</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0363</v>
+        <v>-1.122</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8861</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1312</v>
+        <v>-1.6079</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0547</v>
+        <v>-1.1521</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0765</v>
+        <v>-0.4558</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7912</v>
+        <v>1.3513</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0184</v>
+        <v>0.0302</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8096</v>
+        <v>1.3212</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6525</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R14" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S14" t="n">
-        <v>2.379</v>
+        <v>0.7643</v>
       </c>
       <c r="T14" t="n">
-        <v>2.7988</v>
+        <v>0.1514</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4198</v>
+        <v>0.6128</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.9347</v>
+        <v>1.5204</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1952</v>
+        <v>2.6504</v>
       </c>
       <c r="X14" t="n">
         <v>-1.13</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. POLANCO TAVAREZ</t>
+          <t>B. COULIBALY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6458</v>
+        <v>0.2061</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6458</v>
+        <v>0.4731</v>
       </c>
       <c r="F15" t="n">
-        <v>2.2916</v>
+        <v>-0.267</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2566</v>
+        <v>0.9224</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.122</v>
+        <v>0.0363</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.8861</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.6079</v>
+        <v>0.1312</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.1521</v>
+        <v>0.0547</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.4558</v>
+        <v>0.0765</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3513</v>
+        <v>0.7912</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0302</v>
+        <v>-0.0184</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3212</v>
+        <v>0.8096</v>
       </c>
       <c r="P15" t="n">
+        <v>-0.6525</v>
+      </c>
+      <c r="Q15" t="n">
         <v>-1.0875</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-2.1751</v>
-      </c>
       <c r="R15" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4694</v>
+        <v>0.8709</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4867</v>
+        <v>1.2342</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9827</v>
+        <v>-0.3632</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5204</v>
+        <v>-0.9347</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6504</v>
+        <v>0.1952</v>
       </c>
       <c r="X15" t="n">
         <v>-1.13</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Y. JOSEPH</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1794</v>
+        <v>-0.6644</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9222</v>
+        <v>1.5906</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.1016</v>
+        <v>-2.255</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7144</v>
+        <v>0.8303</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4075</v>
+        <v>-0.1339</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3068</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8691</v>
+        <v>2.2345</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4594</v>
+        <v>0.1674</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4097</v>
+        <v>2.0671</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1548</v>
+        <v>-1.4042</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0519</v>
+        <v>-0.3013</v>
       </c>
       <c r="O16" t="n">
         <v>-1.1029</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.9576</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7588</v>
+        <v>-0.1472</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2281</v>
+        <v>-0.1214</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4694</v>
+        <v>-0.0258</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.695</v>
+        <v>-1.13</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X16" t="n">
         <v>-1.695</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>D. GEU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8924</v>
+        <v>-1.3152</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6965</v>
+        <v>-0.5571</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5889</v>
+        <v>-0.7581</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8303</v>
+        <v>-0.8013</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1339</v>
+        <v>-0.7392</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9641999999999999</v>
+        <v>-0.0622</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2345</v>
+        <v>-0.0601</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1674</v>
+        <v>-0.6538</v>
       </c>
       <c r="L17" t="n">
-        <v>2.0671</v>
+        <v>0.5937</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4042</v>
+        <v>-0.7412</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3013</v>
+        <v>-0.0854</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1029</v>
+        <v>-0.6558</v>
       </c>
       <c r="P17" t="n">
         <v>-0.2175</v>
@@ -1780,28 +1780,28 @@
         <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3752</v>
+        <v>0.6384</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0154</v>
+        <v>0.3954</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3598</v>
+        <v>0.243</v>
       </c>
       <c r="V17" t="n">
+        <v>-0.9347</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="X17" t="n">
         <v>-1.13</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="X17" t="n">
-        <v>-1.695</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. GEU</t>
+          <t>Y. JOSEPH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.041</v>
+        <v>-1.3169</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8924</v>
+        <v>1.3634</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1486</v>
+        <v>-2.6803</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8013</v>
+        <v>1.7144</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7392</v>
+        <v>0.4075</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0622</v>
+        <v>1.3068</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0601</v>
+        <v>2.8691</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6538</v>
+        <v>0.4594</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5937</v>
+        <v>2.4097</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7412</v>
+        <v>-1.1548</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0854</v>
+        <v>-0.0519</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6558</v>
+        <v>-1.1029</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2175</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R18" t="n">
-        <v>0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.08740000000000001</v>
+        <v>0.6213</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0601</v>
+        <v>0.6694</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1475</v>
+        <v>-0.0481</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9347</v>
+        <v>-1.695</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.13</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. TAMBA VILLEN</t>
+          <t>J. BONE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.621</v>
+        <v>-1.4549</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4781</v>
+        <v>-1.6447</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1429</v>
+        <v>0.1897</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5236</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5236</v>
+        <v>-1.9497</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1.8782</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4901</v>
+        <v>-0.4593</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.4901</v>
+        <v>-1.3989</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.9395</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0335</v>
+        <v>0.3879</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0335</v>
+        <v>-0.5508</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.9387</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0326</v>
+        <v>-0.1241</v>
       </c>
       <c r="T19" t="n">
-        <v>0.012</v>
+        <v>-0.4458</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0205</v>
+        <v>0.3217</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.13</v>
+        <v>-2.9995</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.13</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. LARSEN</t>
+          <t>I. TAMBA VILLEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8095</v>
+        <v>-2.5902</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.7209</v>
+        <v>-1.4781</v>
       </c>
       <c r="F20" t="n">
-        <v>2.9114</v>
+        <v>-1.1121</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.4171</v>
+        <v>-1.5236</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3349</v>
+        <v>-1.5236</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0822</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.373</v>
+        <v>-1.4901</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.1156</v>
+        <v>-1.4901</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2574</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0441</v>
+        <v>-0.0335</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2193</v>
+        <v>-0.0335</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8248</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7401</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.6081</v>
+        <v>0.0634</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0853</v>
+        <v>0.012</v>
       </c>
       <c r="U20" t="n">
-        <v>1.6934</v>
+        <v>0.0514</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.7395</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BONE</t>
+          <t>K. LARSEN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8499</v>
+        <v>-3.3271</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7622</v>
+        <v>-5.8327</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0877</v>
+        <v>2.5056</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-3.4171</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9497</v>
+        <v>-1.3349</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8782</v>
+        <v>-2.0822</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4593</v>
+        <v>-2.373</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3989</v>
+        <v>-1.1156</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9395</v>
+        <v>-1.2574</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3879</v>
+        <v>-1.0441</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5508</v>
+        <v>-0.2193</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9387</v>
+        <v>-0.8248</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7401</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5191</v>
+        <v>1.0905</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.5634</v>
+        <v>-0.1971</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0443</v>
+        <v>1.2876</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.9995</v>
+        <v>0.7395</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.2599</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.6116</v>
+        <v>-4.092</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.6187</v>
+        <v>-3.6129</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9929</v>
+        <v>-0.4791</v>
       </c>
       <c r="G22" t="n">
         <v>-4.9931</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1612</v>
+        <v>0.3584</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.2524</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4077</v>
+        <v>0.106</v>
       </c>
       <c r="V22" t="n">
         <v>0.7602</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.586100000000001</v>
+        <v>-6.0962</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.013099999999998</v>
+        <v>-8.013199999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4269999999999997</v>
+        <v>1.917</v>
       </c>
       <c r="G23" t="n">
         <v>-4.4627</v>
@@ -2221,13 +2221,13 @@
         <v>4.569899999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.1982</v>
+        <v>-3.198199999999999</v>
       </c>
       <c r="K23" t="n">
         <v>-7.8443</v>
       </c>
       <c r="L23" t="n">
-        <v>4.6459</v>
+        <v>4.645899999999999</v>
       </c>
       <c r="M23" t="n">
         <v>-1.2645</v>
@@ -2236,7 +2236,7 @@
         <v>-1.1885</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0759000000000003</v>
+        <v>-0.07590000000000052</v>
       </c>
       <c r="P23" t="n">
         <v>-2.1751</v>
@@ -2248,22 +2248,22 @@
         <v>9.787599999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>3.725300000000001</v>
+        <v>5.215299999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>2.391500000000001</v>
+        <v>2.3915</v>
       </c>
       <c r="U23" t="n">
-        <v>1.3336</v>
+        <v>2.8238</v>
       </c>
       <c r="V23" t="n">
         <v>-4.673799999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>4.756499999999999</v>
+        <v>4.7565</v>
       </c>
       <c r="X23" t="n">
-        <v>-9.430400000000001</v>
+        <v>-9.430399999999999</v>
       </c>
     </row>
   </sheetData>
